--- a/data/trans_orig/P63C-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P63C-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la categoría profesional que tiene o tenía en la empresa donde trabaja o trabajaba en 2007</t>
+          <t>Población según la categoría profesional que tiene o tenía en la empresa donde trabaja o trabajaba en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>700699</t>
+          <t>699325</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>756524</t>
+          <t>756469</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>493471</t>
+          <t>493059</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>529091</t>
+          <t>528947</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1209190</t>
+          <t>1209404</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1275859</t>
+          <t>1273710</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>78,95%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36644</t>
+          <t>37002</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65550</t>
+          <t>65750</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>938</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11508</t>
+          <t>12267</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40043</t>
+          <t>39642</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>68847</t>
+          <t>69690</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>837</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8932</t>
+          <t>8100</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>837</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7883</t>
+          <t>7875</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5832</t>
+          <t>6622</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,62 +1107,62 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1909</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>6725</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1909</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>5780</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,42%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19119</t>
+          <t>18845</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39837</t>
+          <t>38887</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5421</t>
+          <t>5440</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18574</t>
+          <t>18244</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>28355</t>
+          <t>27742</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>53437</t>
+          <t>51222</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>2995</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13875</t>
+          <t>13016</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>2959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13386</t>
+          <t>13737</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>149126</t>
+          <t>149323</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>197426</t>
+          <t>197196</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1426,12 +1426,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,12 +1446,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79557</t>
+          <t>78379</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>112998</t>
+          <t>113315</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>236206</t>
+          <t>238879</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>297666</t>
+          <t>299695</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1496,12 +1496,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,58%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1097001</t>
+          <t>1095357</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1160544</t>
+          <t>1159721</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>918314</t>
+          <t>919190</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>965856</t>
+          <t>965905</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2031357</t>
+          <t>2030204</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2111879</t>
+          <t>2111020</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,42%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66564</t>
+          <t>66569</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>99963</t>
+          <t>100195</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11704</t>
+          <t>10994</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29425</t>
+          <t>28954</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82516</t>
+          <t>80965</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>120144</t>
+          <t>120413</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6229</t>
+          <t>5834</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20084</t>
+          <t>20145</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>955</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9755</t>
+          <t>9198</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8839</t>
+          <t>8625</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25193</t>
+          <t>24898</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16075</t>
+          <t>16427</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7402</t>
+          <t>7279</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>5529</t>
+          <t>5082</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>18665</t>
+          <t>18826</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2093,12 +2093,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>68191</t>
+          <t>67963</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>103339</t>
+          <t>103043</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15555</t>
+          <t>15967</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35544</t>
+          <t>35933</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2143,12 +2143,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>90352</t>
+          <t>90148</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>133092</t>
+          <t>131059</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2178,12 +2178,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -2206,12 +2206,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12465</t>
+          <t>12035</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32644</t>
+          <t>32411</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2221,12 +2221,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,12 +2241,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7918</t>
+          <t>7873</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2276,12 +2276,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14411</t>
+          <t>14357</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35917</t>
+          <t>34522</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -2319,12 +2319,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>112699</t>
+          <t>112182</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>157530</t>
+          <t>158363</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2334,12 +2334,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>77953</t>
+          <t>77796</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>116763</t>
+          <t>117011</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>201688</t>
+          <t>201064</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>260194</t>
+          <t>263065</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>321324</t>
+          <t>320181</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>366146</t>
+          <t>365780</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>338597</t>
+          <t>338227</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>366941</t>
+          <t>368022</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>668860</t>
+          <t>667343</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>721741</t>
+          <t>725824</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,78%</t>
         </is>
       </c>
     </row>
@@ -2662,12 +2662,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>44193</t>
+          <t>44991</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>73637</t>
+          <t>73816</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2677,12 +2677,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9534</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>26389</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>59605</t>
+          <t>58589</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>94136</t>
+          <t>94233</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2989</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15773</t>
+          <t>15013</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6461</t>
+          <t>6574</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3687</t>
+          <t>3892</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17137</t>
+          <t>17341</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -2888,12 +2888,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>10864</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>28725</t>
+          <t>28324</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2923,12 +2923,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>927</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8822</t>
+          <t>9596</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2958,12 +2958,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>13032</t>
+          <t>13122</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>32641</t>
+          <t>33043</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -3001,12 +3001,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>36325</t>
+          <t>36872</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>64668</t>
+          <t>64514</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3016,12 +3016,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9935</t>
+          <t>10188</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26086</t>
+          <t>26228</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3051,12 +3051,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>49611</t>
+          <t>49671</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>82318</t>
+          <t>82218</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -3114,12 +3114,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3539</t>
+          <t>3377</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17803</t>
+          <t>17207</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3129,12 +3129,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>991</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10526</t>
+          <t>9513</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3164,12 +3164,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6304</t>
+          <t>6511</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20951</t>
+          <t>22889</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3199,12 +3199,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -3227,12 +3227,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>24656</t>
+          <t>24940</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>48245</t>
+          <t>47037</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10203</t>
+          <t>11261</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>28400</t>
+          <t>29037</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3277,12 +3277,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>38784</t>
+          <t>38559</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>69702</t>
+          <t>68401</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3312,12 +3312,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3457,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2149616</t>
+          <t>2157480</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2248314</t>
+          <t>2253321</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3472,12 +3472,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1777770</t>
+          <t>1777986</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1842950</t>
+          <t>1841197</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3507,12 +3507,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3955161</t>
+          <t>3949496</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4072191</t>
+          <t>4068977</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>79,66%</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3570,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>165263</t>
+          <t>162817</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>216910</t>
+          <t>215447</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>28385</t>
+          <t>28678</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>52426</t>
+          <t>54830</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>200562</t>
+          <t>200431</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>259748</t>
+          <t>257676</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3655,12 +3655,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -3683,12 +3683,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>13326</t>
+          <t>13960</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>32568</t>
+          <t>32785</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>12053</t>
+          <t>12498</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,12 +3753,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>17333</t>
+          <t>18117</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>40559</t>
+          <t>39532</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -3796,12 +3796,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>18448</t>
+          <t>19203</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>40879</t>
+          <t>42381</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3811,12 +3811,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>12058</t>
+          <t>11339</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,12 +3866,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>22698</t>
+          <t>22528</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>46973</t>
+          <t>46577</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -3909,12 +3909,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>137630</t>
+          <t>138241</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>190169</t>
+          <t>187256</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3924,12 +3924,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>38895</t>
+          <t>39170</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>68414</t>
+          <t>67510</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,12 +3979,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>186869</t>
+          <t>187033</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>243434</t>
+          <t>245023</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -4022,12 +4022,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>23907</t>
+          <t>23133</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>50012</t>
+          <t>48517</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4037,12 +4037,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4057,12 +4057,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3153</t>
+          <t>2995</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>15359</t>
+          <t>15316</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>30488</t>
+          <t>30265</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>58661</t>
+          <t>58503</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>304977</t>
+          <t>306459</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>374668</t>
+          <t>376680</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4150,12 +4150,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>184257</t>
+          <t>181362</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>239020</t>
+          <t>240833</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>509567</t>
+          <t>509500</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>597537</t>
+          <t>599890</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,74%</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4401,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la categoría profesional que tiene o tenía en la empresa donde trabaja o trabajaba en 2012</t>
+          <t>Población según la categoría profesional que tiene o tenía en la empresa donde trabaja o trabajaba en 2012 (tasa de respuesta: 99,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4596,12 +4596,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>701202</t>
+          <t>704047</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>755516</t>
+          <t>757854</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>590470</t>
+          <t>590257</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>632033</t>
+          <t>631259</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1310960</t>
+          <t>1309847</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1376666</t>
+          <t>1377268</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,88%</t>
         </is>
       </c>
     </row>
@@ -4709,12 +4709,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14447</t>
+          <t>15675</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35056</t>
+          <t>35079</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4724,12 +4724,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7151</t>
+          <t>7473</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17490</t>
+          <t>17299</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37621</t>
+          <t>38764</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4794,12 +4794,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -4827,7 +4827,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6236</t>
+          <t>6967</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6905</t>
+          <t>6936</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9965</t>
+          <t>9668</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11985</t>
+          <t>10936</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6933</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14971</t>
+          <t>13786</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14351</t>
+          <t>13848</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>34118</t>
+          <t>33157</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4210</t>
+          <t>4918</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17167</t>
+          <t>16637</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>21870</t>
+          <t>20829</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>45071</t>
+          <t>45290</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5188</t>
+          <t>4941</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18546</t>
+          <t>18612</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11544</t>
+          <t>11573</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>8983</t>
+          <t>8901</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>24614</t>
+          <t>24611</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>134058</t>
+          <t>135173</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>180968</t>
+          <t>180391</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>82278</t>
+          <t>82701</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>121239</t>
+          <t>120463</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>223581</t>
+          <t>226797</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>285514</t>
+          <t>289181</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,19%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1308643</t>
+          <t>1306730</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1382643</t>
+          <t>1377879</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1097483</t>
+          <t>1100114</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1149279</t>
+          <t>1150103</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2423032</t>
+          <t>2422308</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2509738</t>
+          <t>2514594</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,73%</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72423</t>
+          <t>74974</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>113240</t>
+          <t>114749</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19349</t>
+          <t>20017</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42690</t>
+          <t>44482</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>101930</t>
+          <t>97852</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>148370</t>
+          <t>146403</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10244</t>
+          <t>10856</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29649</t>
+          <t>30259</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3347</t>
+          <t>3285</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17288</t>
+          <t>16630</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17396</t>
+          <t>17146</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>43196</t>
+          <t>41199</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>4556</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22956</t>
+          <t>20380</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5883,7 +5883,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>5660</t>
+          <t>5389</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>22653</t>
+          <t>21442</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43680</t>
+          <t>44329</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>71846</t>
+          <t>73216</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13941</t>
+          <t>14405</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33203</t>
+          <t>33731</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>63936</t>
+          <t>64151</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>99059</t>
+          <t>97475</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -6069,12 +6069,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9927</t>
+          <t>11365</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29719</t>
+          <t>30898</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6104,12 +6104,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4157</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19270</t>
+          <t>20159</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6139,12 +6139,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18451</t>
+          <t>18746</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41916</t>
+          <t>42723</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6154,12 +6154,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -6182,12 +6182,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>165109</t>
+          <t>168059</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>218829</t>
+          <t>222180</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>86511</t>
+          <t>86672</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>124935</t>
+          <t>127699</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6232,12 +6232,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6252,12 +6252,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>269897</t>
+          <t>269313</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>333578</t>
+          <t>341117</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6267,12 +6267,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,22%</t>
         </is>
       </c>
     </row>
@@ -6412,12 +6412,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>277280</t>
+          <t>281684</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>321982</t>
+          <t>322942</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6447,12 +6447,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>312203</t>
+          <t>311662</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>342936</t>
+          <t>343945</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>601312</t>
+          <t>602672</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>653330</t>
+          <t>654840</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>78,23%</t>
         </is>
       </c>
     </row>
@@ -6525,12 +6525,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>42745</t>
+          <t>41640</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>75277</t>
+          <t>73752</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6560,12 +6560,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9946</t>
+          <t>9887</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25187</t>
+          <t>26229</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6575,12 +6575,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6595,12 +6595,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>57337</t>
+          <t>55812</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>92822</t>
+          <t>91115</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6610,12 +6610,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -6638,12 +6638,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2898</t>
+          <t>2823</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14791</t>
+          <t>15720</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>973</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>8770</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4972</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18532</t>
+          <t>17976</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -6751,12 +6751,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7908</t>
+          <t>7295</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22114</t>
+          <t>23002</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6766,12 +6766,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7264</t>
+          <t>7537</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8181</t>
+          <t>8597</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>23894</t>
+          <t>25247</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6836,12 +6836,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -6864,12 +6864,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14628</t>
+          <t>14680</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>36887</t>
+          <t>36009</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6879,12 +6879,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6899,12 +6899,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3866</t>
+          <t>3818</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18517</t>
+          <t>19965</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6914,12 +6914,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6934,12 +6934,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>21567</t>
+          <t>21629</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>45868</t>
+          <t>46792</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -6977,12 +6977,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5298</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19153</t>
+          <t>20631</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7012,12 +7012,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>885</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8343</t>
+          <t>8796</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8343</t>
+          <t>7857</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>24932</t>
+          <t>23979</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7062,12 +7062,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -7090,12 +7090,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>23819</t>
+          <t>25413</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>49861</t>
+          <t>49665</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7105,12 +7105,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7125,12 +7125,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>17956</t>
+          <t>19294</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>42462</t>
+          <t>44083</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>49212</t>
+          <t>47976</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>80786</t>
+          <t>80350</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -7320,12 +7320,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2326861</t>
+          <t>2328910</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2427412</t>
+          <t>2426946</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7335,12 +7335,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7355,12 +7355,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2030175</t>
+          <t>2030768</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2102708</t>
+          <t>2104628</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7370,12 +7370,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4378843</t>
+          <t>4375981</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4507983</t>
+          <t>4506799</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7405,12 +7405,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>81,08%</t>
         </is>
       </c>
     </row>
@@ -7433,12 +7433,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>147480</t>
+          <t>146245</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>201000</t>
+          <t>202218</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7468,12 +7468,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>35449</t>
+          <t>35469</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>64674</t>
+          <t>64432</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7488,7 +7488,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>190977</t>
+          <t>191587</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>253729</t>
+          <t>254906</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7518,12 +7518,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -7546,12 +7546,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>17920</t>
+          <t>17928</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>41284</t>
+          <t>40698</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7581,12 +7581,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6644</t>
+          <t>7087</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>23398</t>
+          <t>23006</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>28365</t>
+          <t>29115</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>55703</t>
+          <t>56843</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -7659,12 +7659,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>17367</t>
+          <t>17139</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>39706</t>
+          <t>40065</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2108</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>12113</t>
+          <t>11738</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>20414</t>
+          <t>21517</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>44930</t>
+          <t>45861</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -7772,12 +7772,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>85173</t>
+          <t>83346</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>125767</t>
+          <t>125197</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>28545</t>
+          <t>29233</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>53422</t>
+          <t>54599</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>121839</t>
+          <t>121070</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>168800</t>
+          <t>171091</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -7885,12 +7885,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>29371</t>
+          <t>28711</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>55767</t>
+          <t>54430</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>10240</t>
+          <t>10302</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>29561</t>
+          <t>28916</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7940,7 +7940,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7955,12 +7955,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>43303</t>
+          <t>43299</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>76419</t>
+          <t>78261</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -7975,7 +7975,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -7998,12 +7998,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>348597</t>
+          <t>349156</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>425957</t>
+          <t>425277</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8013,12 +8013,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8033,12 +8033,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>205521</t>
+          <t>203903</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>263851</t>
+          <t>264338</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8068,12 +8068,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>576728</t>
+          <t>571532</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>669609</t>
+          <t>670929</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -8264,7 +8264,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la categoría profesional que tiene o tenía en la empresa donde trabaja o trabajaba en 2016</t>
+          <t>Población según la categoría profesional que tiene o tenía en la empresa donde trabaja o trabajaba en 2016 (tasa de respuesta: 98,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8459,12 +8459,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>555771</t>
+          <t>556181</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>600216</t>
+          <t>598388</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8474,12 +8474,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8494,12 +8494,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>439192</t>
+          <t>439049</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>467585</t>
+          <t>468401</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8509,12 +8509,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8529,12 +8529,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1005143</t>
+          <t>1006493</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1057232</t>
+          <t>1058249</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8544,12 +8544,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,19%</t>
         </is>
       </c>
     </row>
@@ -8572,12 +8572,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16136</t>
+          <t>17054</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36132</t>
+          <t>36032</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8587,12 +8587,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8607,12 +8607,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11652</t>
+          <t>11386</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8622,47 +8622,47 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>28408</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>19013</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>40940</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
           <t>2,29%</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>28408</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>19162</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>39725</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5498</t>
+          <t>5486</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8725,7 +8725,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6648</t>
+          <t>6737</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>785</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8540</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8775,7 +8775,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -8803,7 +8803,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5803</t>
+          <t>5748</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8818,7 +8818,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8838,7 +8838,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5830</t>
+          <t>3899</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8853,7 +8853,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8868,12 +8868,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>762</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>7396</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8888,7 +8888,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -8911,12 +8911,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7496</t>
+          <t>6950</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22343</t>
+          <t>22437</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8926,12 +8926,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>881</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10507</t>
+          <t>10422</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8811</t>
+          <t>9953</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>26391</t>
+          <t>27030</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -9024,12 +9024,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3247</t>
+          <t>3348</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13648</t>
+          <t>14977</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9039,12 +9039,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9059,12 +9059,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9073</t>
+          <t>10124</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9079,7 +9079,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6380</t>
+          <t>5187</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>20083</t>
+          <t>18805</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -9137,12 +9137,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>87673</t>
+          <t>88501</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>124464</t>
+          <t>125131</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9152,12 +9152,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9172,12 +9172,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30869</t>
+          <t>29978</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55560</t>
+          <t>55653</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9207,12 +9207,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>127106</t>
+          <t>127173</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>170757</t>
+          <t>173139</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -9367,12 +9367,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1417031</t>
+          <t>1411661</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1488856</t>
+          <t>1484986</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9382,12 +9382,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9402,12 +9402,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1211324</t>
+          <t>1209855</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1263851</t>
+          <t>1264555</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9417,12 +9417,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9437,12 +9437,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2648350</t>
+          <t>2638971</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2738014</t>
+          <t>2732588</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>83,96%</t>
         </is>
       </c>
     </row>
@@ -9480,12 +9480,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59027</t>
+          <t>59827</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95110</t>
+          <t>97108</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9495,12 +9495,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9515,12 +9515,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12058</t>
+          <t>12590</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32222</t>
+          <t>31422</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9530,12 +9530,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9550,12 +9550,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>78492</t>
+          <t>78583</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>118482</t>
+          <t>120774</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9570,7 +9570,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -9593,12 +9593,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6184</t>
+          <t>6470</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21092</t>
+          <t>21802</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9608,12 +9608,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8532</t>
+          <t>6765</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9663,12 +9663,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7757</t>
+          <t>7958</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23640</t>
+          <t>24437</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9683,7 +9683,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -9706,12 +9706,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9131</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26798</t>
+          <t>26992</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9721,12 +9721,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6994</t>
+          <t>7745</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9761,7 +9761,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9776,12 +9776,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>9726</t>
+          <t>9709</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>29722</t>
+          <t>28868</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9796,7 +9796,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -9819,12 +9819,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30748</t>
+          <t>30935</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57455</t>
+          <t>57201</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9834,12 +9834,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9854,12 +9854,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12316</t>
+          <t>11660</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30716</t>
+          <t>29272</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9869,12 +9869,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9889,12 +9889,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47703</t>
+          <t>48621</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>79087</t>
+          <t>79919</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -9932,12 +9932,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8785</t>
+          <t>8457</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27077</t>
+          <t>26553</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9947,12 +9947,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4981</t>
+          <t>4729</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19804</t>
+          <t>18440</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9982,12 +9982,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10002,12 +10002,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16852</t>
+          <t>16306</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37311</t>
+          <t>38019</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -10045,12 +10045,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>191912</t>
+          <t>193391</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>247891</t>
+          <t>248809</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>109169</t>
+          <t>110849</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>152640</t>
+          <t>154751</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10115,12 +10115,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>311536</t>
+          <t>317079</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>384256</t>
+          <t>390260</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -10275,12 +10275,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>324708</t>
+          <t>324413</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>367738</t>
+          <t>366240</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10290,12 +10290,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10310,12 +10310,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>383626</t>
+          <t>382287</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>415933</t>
+          <t>416125</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10325,12 +10325,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10345,12 +10345,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>718100</t>
+          <t>715809</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>770935</t>
+          <t>772697</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,37%</t>
         </is>
       </c>
     </row>
@@ -10388,12 +10388,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>36522</t>
+          <t>37728</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>66940</t>
+          <t>67380</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15023</t>
+          <t>15720</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>35036</t>
+          <t>34781</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10458,12 +10458,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>60359</t>
+          <t>58162</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>94732</t>
+          <t>94825</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10473,12 +10473,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -10501,12 +10501,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2545</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14149</t>
+          <t>13090</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1786</t>
+          <t>1873</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11601</t>
+          <t>11247</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10571,12 +10571,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6062</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>19746</t>
+          <t>19301</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -10614,12 +10614,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11339</t>
+          <t>13015</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6958</t>
+          <t>6988</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10684,12 +10684,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2843</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>13732</t>
+          <t>15408</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10699,12 +10699,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -10727,12 +10727,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8322</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24227</t>
+          <t>24603</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10747,7 +10747,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10762,12 +10762,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7520</t>
+          <t>7460</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23444</t>
+          <t>24004</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10777,12 +10777,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10797,12 +10797,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>19383</t>
+          <t>19378</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>41468</t>
+          <t>41576</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10817,7 +10817,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -10840,12 +10840,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3897</t>
+          <t>4236</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17085</t>
+          <t>19500</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10855,12 +10855,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10880,7 +10880,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5638</t>
+          <t>4926</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10895,7 +10895,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10910,12 +10910,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4497</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19907</t>
+          <t>21006</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10925,12 +10925,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -10953,12 +10953,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>46576</t>
+          <t>47910</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>78606</t>
+          <t>77219</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10968,12 +10968,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10988,12 +10988,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>21812</t>
+          <t>22304</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>43745</t>
+          <t>45438</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11003,12 +11003,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11023,12 +11023,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>75796</t>
+          <t>77018</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>113369</t>
+          <t>114316</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11038,12 +11038,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,74%</t>
         </is>
       </c>
     </row>
@@ -11183,12 +11183,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2332811</t>
+          <t>2334170</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2427426</t>
+          <t>2428111</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11218,12 +11218,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2060461</t>
+          <t>2057617</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2123906</t>
+          <t>2123728</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11233,7 +11233,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -11253,12 +11253,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4411339</t>
+          <t>4409514</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4523229</t>
+          <t>4529031</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11268,12 +11268,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,79%</t>
         </is>
       </c>
     </row>
@@ -11296,12 +11296,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>129125</t>
+          <t>127751</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>178068</t>
+          <t>178365</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11311,12 +11311,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11331,12 +11331,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>35034</t>
+          <t>33815</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>64390</t>
+          <t>62624</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11366,12 +11366,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>171857</t>
+          <t>171497</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>227633</t>
+          <t>229531</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11386,7 +11386,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -11409,12 +11409,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>12456</t>
+          <t>12926</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>30936</t>
+          <t>30474</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11424,12 +11424,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11444,12 +11444,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3909</t>
+          <t>4044</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>16639</t>
+          <t>16036</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11459,12 +11459,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>18526</t>
+          <t>19004</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>40855</t>
+          <t>40289</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11494,12 +11494,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -11522,12 +11522,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>13469</t>
+          <t>13470</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>33491</t>
+          <t>34183</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11542,7 +11542,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11557,12 +11557,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>964</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>10875</t>
+          <t>10484</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11577,7 +11577,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11592,12 +11592,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>16704</t>
+          <t>15960</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>38793</t>
+          <t>38686</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11607,7 +11607,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -11635,12 +11635,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>54506</t>
+          <t>56303</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>88082</t>
+          <t>89814</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11670,12 +11670,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>26364</t>
+          <t>25921</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>50634</t>
+          <t>51071</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11685,12 +11685,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11705,12 +11705,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>89544</t>
+          <t>89082</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>131818</t>
+          <t>132082</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11720,7 +11720,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -11748,12 +11748,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>22665</t>
+          <t>21937</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>47957</t>
+          <t>46119</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11783,12 +11783,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>7669</t>
+          <t>7368</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>24395</t>
+          <t>23777</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11818,12 +11818,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>34929</t>
+          <t>33234</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>65088</t>
+          <t>61564</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11833,12 +11833,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -11861,12 +11861,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>348806</t>
+          <t>349172</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>422131</t>
+          <t>422093</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11876,7 +11876,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -11896,12 +11896,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>178037</t>
+          <t>179852</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>232200</t>
+          <t>233174</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11931,12 +11931,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>547567</t>
+          <t>543257</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>638585</t>
+          <t>634478</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -11946,12 +11946,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -12127,7 +12127,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la categoría profesional que tiene o tenía en la empresa donde trabaja o trabajaba en 2023</t>
+          <t>Población según la categoría profesional que tiene o tenía en la empresa donde trabaja o trabajaba en 2023 (tasa de respuesta: 98,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -12322,12 +12322,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>357632</t>
+          <t>358184</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>392607</t>
+          <t>395084</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -12337,12 +12337,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -12357,12 +12357,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>334213</t>
+          <t>332131</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>358789</t>
+          <t>358890</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -12372,12 +12372,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -12392,12 +12392,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>701138</t>
+          <t>697327</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>745821</t>
+          <t>742232</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -12407,12 +12407,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,39%</t>
         </is>
       </c>
     </row>
@@ -12435,12 +12435,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10882</t>
+          <t>11016</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24392</t>
+          <t>24706</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -12450,12 +12450,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -12470,12 +12470,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5623</t>
+          <t>5829</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -12485,12 +12485,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -12505,12 +12505,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12494</t>
+          <t>13065</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27048</t>
+          <t>27885</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -12520,12 +12520,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -12553,7 +12553,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3804</t>
+          <t>4481</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -12568,7 +12568,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -12588,7 +12588,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -12603,7 +12603,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -12623,7 +12623,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>4266</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -12638,7 +12638,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -12661,12 +12661,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>550</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7201</t>
+          <t>6965</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12676,82 +12676,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1567</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>9362</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>3892</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>1267</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>10991</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>0,14%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1567</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>7730</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>3892</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>1102</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>10569</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -12774,12 +12774,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6295</t>
+          <t>6551</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16568</t>
+          <t>17077</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12789,12 +12789,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4154</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12876</t>
+          <t>13630</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12824,12 +12824,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12007</t>
+          <t>11931</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25102</t>
+          <t>25189</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12864,7 +12864,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -12887,12 +12887,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2183</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10221</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12902,12 +12902,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12927,7 +12927,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3043</t>
+          <t>3495</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2587</t>
+          <t>2716</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11647</t>
+          <t>11823</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -12972,12 +12972,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -13000,12 +13000,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>79096</t>
+          <t>77240</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>110618</t>
+          <t>109653</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -13015,12 +13015,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60470</t>
+          <t>58684</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>83401</t>
+          <t>83253</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -13050,12 +13050,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>143155</t>
+          <t>145828</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>184694</t>
+          <t>185980</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -13085,12 +13085,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -13230,12 +13230,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>848839</t>
+          <t>898775</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1543332</t>
+          <t>1541125</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -13245,12 +13245,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -13265,12 +13265,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1308603</t>
+          <t>1303306</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1573430</t>
+          <t>1577658</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -13280,12 +13280,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -13300,12 +13300,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2277048</t>
+          <t>2144931</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3078127</t>
+          <t>3086145</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -13315,12 +13315,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,83%</t>
         </is>
       </c>
     </row>
@@ -13343,12 +13343,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>94025</t>
+          <t>93068</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>168842</t>
+          <t>171287</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -13358,12 +13358,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -13378,12 +13378,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25910</t>
+          <t>24424</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52884</t>
+          <t>51498</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -13393,12 +13393,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>134159</t>
+          <t>131962</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>211881</t>
+          <t>213272</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -13428,12 +13428,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -13461,7 +13461,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6668</t>
+          <t>6831</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7426</t>
+          <t>7932</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -13506,12 +13506,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2770</t>
+          <t>2431</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11455</t>
+          <t>11217</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -13541,12 +13541,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
     </row>
@@ -13569,12 +13569,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13906</t>
+          <t>11969</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>921717</t>
+          <t>857915</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3606</t>
+          <t>3716</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13533</t>
+          <t>13260</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -13619,12 +13619,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>19362</t>
+          <t>19393</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>933939</t>
+          <t>1079849</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -13659,7 +13659,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>28,28%</t>
         </is>
       </c>
     </row>
@@ -13682,12 +13682,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>47869</t>
+          <t>52000</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>93284</t>
+          <t>95873</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13697,12 +13697,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26283</t>
+          <t>25662</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>344225</t>
+          <t>310017</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13732,12 +13732,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>97697</t>
+          <t>96961</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>422974</t>
+          <t>426188</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13767,12 +13767,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -13795,12 +13795,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10661</t>
+          <t>11340</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29695</t>
+          <t>30993</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13810,12 +13810,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>1811</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8864</t>
+          <t>8575</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13845,12 +13845,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16216</t>
+          <t>16750</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>36891</t>
+          <t>36450</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13880,12 +13880,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -13908,12 +13908,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>133887</t>
+          <t>141753</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>240007</t>
+          <t>246387</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13923,12 +13923,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>92305</t>
+          <t>88444</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>165049</t>
+          <t>162127</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13958,12 +13958,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>257899</t>
+          <t>263252</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>390791</t>
+          <t>394384</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13993,12 +13993,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -14138,12 +14138,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>352637</t>
+          <t>351703</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>401269</t>
+          <t>403396</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -14153,12 +14153,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>449780</t>
+          <t>449490</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>482399</t>
+          <t>484188</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>815139</t>
+          <t>814504</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>874835</t>
+          <t>876404</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -14223,12 +14223,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,24%</t>
         </is>
       </c>
     </row>
@@ -14251,12 +14251,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>73203</t>
+          <t>71259</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>106053</t>
+          <t>106794</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -14266,12 +14266,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>43142</t>
+          <t>42497</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>66806</t>
+          <t>66055</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -14301,12 +14301,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>122797</t>
+          <t>121897</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>164352</t>
+          <t>165875</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -14336,12 +14336,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,67%</t>
         </is>
       </c>
     </row>
@@ -14364,12 +14364,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6922</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20021</t>
+          <t>19882</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -14379,12 +14379,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>675</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>6900</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -14419,7 +14419,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8774</t>
+          <t>8789</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22471</t>
+          <t>24101</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -14454,7 +14454,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -14477,12 +14477,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9339</t>
+          <t>9091</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>28070</t>
+          <t>27795</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -14492,12 +14492,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3837</t>
+          <t>3829</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>13638</t>
+          <t>13263</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -14532,7 +14532,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>15899</t>
+          <t>15106</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>37351</t>
+          <t>37471</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -14562,12 +14562,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -14590,12 +14590,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13905</t>
+          <t>13961</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>30695</t>
+          <t>30714</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -14605,7 +14605,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10326</t>
+          <t>10620</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22783</t>
+          <t>23202</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -14640,12 +14640,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>27538</t>
+          <t>28123</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>48290</t>
+          <t>49173</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -14703,12 +14703,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6170</t>
+          <t>6258</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19467</t>
+          <t>20038</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14718,12 +14718,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14738,12 +14738,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1178</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6796</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14753,12 +14753,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14773,12 +14773,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8968</t>
+          <t>8634</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23836</t>
+          <t>23371</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14788,12 +14788,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -14816,12 +14816,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>60928</t>
+          <t>61191</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>95420</t>
+          <t>94486</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14831,12 +14831,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14851,12 +14851,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>48252</t>
+          <t>49269</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>71816</t>
+          <t>74159</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14866,12 +14866,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14886,12 +14886,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>117016</t>
+          <t>116427</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>158456</t>
+          <t>157296</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14901,12 +14901,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -15046,12 +15046,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1674718</t>
+          <t>1601105</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2290753</t>
+          <t>2292635</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -15061,12 +15061,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2101783</t>
+          <t>2098257</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2398279</t>
+          <t>2401829</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -15096,12 +15096,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3702336</t>
+          <t>3810148</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4650820</t>
+          <t>4638392</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -15131,12 +15131,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>77,74%</t>
         </is>
       </c>
     </row>
@@ -15159,12 +15159,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>185649</t>
+          <t>190079</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>282293</t>
+          <t>280727</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -15174,12 +15174,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>73172</t>
+          <t>73077</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>113738</t>
+          <t>113010</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -15209,12 +15209,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>284683</t>
+          <t>280693</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>383833</t>
+          <t>380235</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -15244,12 +15244,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -15272,12 +15272,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>8393</t>
+          <t>8867</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>23451</t>
+          <t>24291</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -15287,12 +15287,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3388</t>
+          <t>3519</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>12635</t>
+          <t>12137</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -15327,7 +15327,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>14449</t>
+          <t>14375</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>31593</t>
+          <t>30829</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -15362,7 +15362,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -15385,12 +15385,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>31166</t>
+          <t>31039</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>833674</t>
+          <t>957588</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -15405,7 +15405,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -15420,12 +15420,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>10040</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>25401</t>
+          <t>25294</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -15435,7 +15435,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -15455,12 +15455,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>45178</t>
+          <t>46935</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1298996</t>
+          <t>1019012</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -15470,12 +15470,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>17,08%</t>
         </is>
       </c>
     </row>
@@ -15498,12 +15498,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>82686</t>
+          <t>80253</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>128646</t>
+          <t>130150</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -15513,12 +15513,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -15533,12 +15533,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>49115</t>
+          <t>47540</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>367637</t>
+          <t>374540</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -15548,12 +15548,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -15568,12 +15568,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>153483</t>
+          <t>151698</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>494509</t>
+          <t>507643</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -15583,12 +15583,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -15611,12 +15611,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>25707</t>
+          <t>25592</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>49513</t>
+          <t>50205</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -15626,12 +15626,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -15646,12 +15646,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>4731</t>
+          <t>4567</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>14077</t>
+          <t>14187</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15661,7 +15661,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -15681,12 +15681,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>32799</t>
+          <t>32727</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>59501</t>
+          <t>58381</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -15701,7 +15701,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -15724,12 +15724,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>280245</t>
+          <t>286746</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>418425</t>
+          <t>420366</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -15739,12 +15739,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -15759,12 +15759,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>210701</t>
+          <t>207147</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>301364</t>
+          <t>301716</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -15774,12 +15774,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -15794,12 +15794,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>529418</t>
+          <t>542550</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>699344</t>
+          <t>703045</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -15809,12 +15809,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,78%</t>
         </is>
       </c>
     </row>
